--- a/grupos/3ALCV - Estadisticos 20221.xlsx
+++ b/grupos/3ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -200,15 +200,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
@@ -239,6 +239,117 @@
     <t>CAMARILLO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>CORDOVA</t>
   </si>
   <si>
@@ -251,25 +362,10 @@
     <t>ELPIDIO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>MERINO</t>
   </si>
   <si>
     <t>MORALES</t>
@@ -281,18 +377,9 @@
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -302,33 +389,18 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>SORIANO</t>
   </si>
   <si>
     <t>TENTZOHUA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
@@ -338,21 +410,9 @@
     <t>ARIAS</t>
   </si>
   <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>VALIENTE</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
@@ -362,48 +422,27 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
     <t>HIPOLITO</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
     <t>QUIÑONES</t>
   </si>
   <si>
-    <t>MENA</t>
-  </si>
-  <si>
     <t>PORRAS</t>
   </si>
   <si>
     <t>LEÓN</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>MACARIO</t>
   </si>
   <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
     <t>CRISTAL YOSELIN</t>
   </si>
   <si>
@@ -419,21 +458,9 @@
     <t>YARED</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
     <t>BERENICE</t>
   </si>
   <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
     <t>REGINA ISABEL</t>
   </si>
   <si>
@@ -449,6 +476,9 @@
     <t>JOSE ISAAC</t>
   </si>
   <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
     <t>FATIMA MARILYN</t>
   </si>
   <si>
@@ -458,24 +488,12 @@
     <t>ITZEL ABIGAIL</t>
   </si>
   <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
     <t>JAZMIN</t>
   </si>
   <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
     <t>LUIS REY</t>
   </si>
   <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
     <t>CITLALI ESPERANZA</t>
   </si>
   <si>
@@ -485,34 +503,16 @@
     <t>ANGEL DAVID</t>
   </si>
   <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
     <t>GABRIELA</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
     <t>KAREN</t>
   </si>
   <si>
     <t>RUBI</t>
   </si>
   <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
     <t>FLOR GUADALUPE</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>8</v>
@@ -1064,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1241,7 +1241,7 @@
         <v>9</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>8</v>
@@ -1295,7 +1295,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1395,7 +1395,7 @@
         <v>9</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1472,7 +1472,7 @@
         <v>9</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -1526,7 +1526,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -1603,7 +1603,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1626,7 +1626,7 @@
         <v>9</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>9</v>
@@ -1680,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1703,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>7</v>
@@ -1757,7 +1757,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1780,7 +1780,7 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -1834,7 +1834,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1857,7 +1857,7 @@
         <v>9</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -1911,7 +1911,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1934,7 +1934,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>9</v>
@@ -1988,7 +1988,7 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -2011,7 +2011,7 @@
         <v>6</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -2065,7 +2065,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>-1</v>
@@ -2088,7 +2088,7 @@
         <v>9</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G18">
         <v>6</v>
@@ -2142,7 +2142,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2165,7 +2165,7 @@
         <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>9</v>
@@ -2219,7 +2219,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2242,7 +2242,7 @@
         <v>9</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2319,7 +2319,7 @@
         <v>9</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>6</v>
@@ -2373,7 +2373,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2396,7 +2396,7 @@
         <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>6</v>
@@ -2450,7 +2450,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2473,7 +2473,7 @@
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -2527,7 +2527,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2579,7 +2579,7 @@
         <v>9</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G25">
         <v>8</v>
@@ -2633,7 +2633,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2656,7 +2656,7 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>6</v>
@@ -2710,7 +2710,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2733,7 +2733,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>9</v>
@@ -2787,7 +2787,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2810,7 +2810,7 @@
         <v>9</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G28">
         <v>8</v>
@@ -2864,7 +2864,7 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2887,7 +2887,7 @@
         <v>7</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>9</v>
@@ -2941,7 +2941,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -3041,7 +3041,7 @@
         <v>9</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G31">
         <v>8</v>
@@ -3095,7 +3095,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3118,7 +3118,7 @@
         <v>8</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -3172,7 +3172,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3195,7 +3195,7 @@
         <v>9</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G33">
         <v>6</v>
@@ -3249,7 +3249,7 @@
         <v>9</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3272,7 +3272,7 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G34">
         <v>9</v>
@@ -3326,7 +3326,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3349,7 +3349,7 @@
         <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G35">
         <v>6</v>
@@ -3403,7 +3403,7 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3426,7 +3426,7 @@
         <v>8</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -3480,7 +3480,7 @@
         <v>8</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3503,7 +3503,7 @@
         <v>8</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G37">
         <v>8</v>
@@ -3557,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -3580,7 +3580,7 @@
         <v>5</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>-1</v>
@@ -3634,7 +3634,7 @@
         <v>5</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>-1</v>
@@ -3657,7 +3657,7 @@
         <v>9</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G39">
         <v>9</v>
@@ -3711,7 +3711,7 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>9</v>
@@ -3734,7 +3734,7 @@
         <v>9</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G40">
         <v>8</v>
@@ -3788,7 +3788,7 @@
         <v>9</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -3888,7 +3888,7 @@
         <v>9</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G42">
         <v>9</v>
@@ -3942,7 +3942,7 @@
         <v>9</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y42">
         <v>9</v>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -4010,27 +4010,30 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>71.05</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.1</v>
+      </c>
       <c r="I2">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -4039,30 +4042,30 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>81.58</v>
+      </c>
+      <c r="G3">
+        <v>18.42</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>71.05</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>7.1</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>28.95</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -4071,25 +4074,25 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>81.58</v>
+        <v>89.47</v>
       </c>
       <c r="G4">
-        <v>18.42</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4195,7 +4198,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4230,53 +4233,53 @@
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920072</v>
+        <v>20330051920222</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>60</v>
@@ -4290,16 +4293,16 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4310,16 +4313,16 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4330,16 +4333,16 @@
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4350,53 +4353,53 @@
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920222</v>
+        <v>21330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920074</v>
+        <v>21330051920078</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>60</v>
@@ -4404,39 +4407,39 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920378</v>
+        <v>21330051920260</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920075</v>
+        <v>21330051920082</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>60</v>
@@ -4444,19 +4447,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920108</v>
+        <v>21330051920094</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>60</v>
@@ -4464,59 +4467,59 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920076</v>
+        <v>21330051920096</v>
       </c>
       <c r="B14" t="s">
         <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920077</v>
+        <v>21330051920098</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920077</v>
+        <v>21330051920100</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" t="s">
         <v>106</v>
       </c>
-      <c r="D16" t="s">
-        <v>133</v>
-      </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>60</v>
@@ -4524,39 +4527,39 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920078</v>
+        <v>21330051920103</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" t="s">
         <v>107</v>
       </c>
-      <c r="D17" t="s">
-        <v>134</v>
-      </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920078</v>
+        <v>21330051920105</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>60</v>
@@ -4564,39 +4567,39 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920079</v>
+        <v>21330051920105</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" t="s">
         <v>108</v>
       </c>
-      <c r="D19" t="s">
-        <v>135</v>
-      </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920260</v>
+        <v>21330051920109</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
         <v>109</v>
       </c>
-      <c r="D20" t="s">
-        <v>136</v>
-      </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>60</v>
@@ -4604,722 +4607,42 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920260</v>
+        <v>21330051920109</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
         <v>109</v>
       </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920080</v>
+        <v>21330051920109</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920082</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920082</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920083</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920084</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920085</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920086</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920302</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" t="s">
-        <v>142</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920089</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" t="s">
-        <v>143</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920092</v>
-      </c>
-      <c r="B31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920093</v>
-      </c>
-      <c r="B32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920094</v>
-      </c>
-      <c r="B33" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" t="s">
-        <v>115</v>
-      </c>
-      <c r="D33" t="s">
-        <v>146</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920094</v>
-      </c>
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>115</v>
-      </c>
-      <c r="D34" t="s">
-        <v>146</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920096</v>
-      </c>
-      <c r="B35" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" t="s">
-        <v>116</v>
-      </c>
-      <c r="D35" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920097</v>
-      </c>
-      <c r="B36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s">
-        <v>117</v>
-      </c>
-      <c r="D36" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920098</v>
-      </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" t="s">
-        <v>83</v>
-      </c>
-      <c r="D37" t="s">
-        <v>149</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920098</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" t="s">
-        <v>149</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920099</v>
-      </c>
-      <c r="B39" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920100</v>
-      </c>
-      <c r="B40" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" t="s">
-        <v>151</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920100</v>
-      </c>
-      <c r="B41" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" t="s">
-        <v>151</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920101</v>
-      </c>
-      <c r="B42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" t="s">
-        <v>152</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920383</v>
-      </c>
-      <c r="B43" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" t="s">
-        <v>93</v>
-      </c>
-      <c r="D43" t="s">
-        <v>153</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920102</v>
-      </c>
-      <c r="B44" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" t="s">
-        <v>74</v>
-      </c>
-      <c r="D44" t="s">
-        <v>154</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920103</v>
-      </c>
-      <c r="B45" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" t="s">
-        <v>83</v>
-      </c>
-      <c r="D45" t="s">
-        <v>155</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920103</v>
-      </c>
-      <c r="B46" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" t="s">
-        <v>155</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920104</v>
-      </c>
-      <c r="B47" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47" t="s">
-        <v>119</v>
-      </c>
-      <c r="D47" t="s">
-        <v>156</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920105</v>
-      </c>
-      <c r="B48" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" t="s">
-        <v>157</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920105</v>
-      </c>
-      <c r="B49" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" t="s">
-        <v>120</v>
-      </c>
-      <c r="D49" t="s">
-        <v>157</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920105</v>
-      </c>
-      <c r="B50" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" t="s">
-        <v>120</v>
-      </c>
-      <c r="D50" t="s">
-        <v>157</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920106</v>
-      </c>
-      <c r="B51" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" t="s">
-        <v>121</v>
-      </c>
-      <c r="D51" t="s">
-        <v>158</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920107</v>
-      </c>
-      <c r="B52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" t="s">
-        <v>122</v>
-      </c>
-      <c r="D52" t="s">
-        <v>159</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920109</v>
-      </c>
-      <c r="B53" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" t="s">
-        <v>123</v>
-      </c>
-      <c r="D53" t="s">
-        <v>160</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920109</v>
-      </c>
-      <c r="B54" t="s">
-        <v>99</v>
-      </c>
-      <c r="C54" t="s">
-        <v>123</v>
-      </c>
-      <c r="D54" t="s">
-        <v>160</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920109</v>
-      </c>
-      <c r="B55" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" t="s">
-        <v>123</v>
-      </c>
-      <c r="D55" t="s">
-        <v>160</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920387</v>
-      </c>
-      <c r="B56" t="s">
-        <v>100</v>
-      </c>
-      <c r="C56" t="s">
-        <v>124</v>
-      </c>
-      <c r="D56" t="s">
-        <v>161</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5361,10 +4684,10 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -5372,16 +4695,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920105</v>
+        <v>21330051920109</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5389,19 +4712,19 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920109</v>
+        <v>21330051920105</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5412,163 +4735,163 @@
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920077</v>
+        <v>21330051920072</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920078</v>
+        <v>21330051920077</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920260</v>
+        <v>21330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920082</v>
+        <v>21330051920260</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920094</v>
+        <v>21330051920082</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920098</v>
+        <v>21330051920094</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920100</v>
+        <v>21330051920096</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920103</v>
+        <v>21330051920098</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920072</v>
+        <v>21330051920100</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5576,16 +4899,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920074</v>
+        <v>21330051920103</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -5593,421 +4916,421 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920378</v>
+        <v>21330051920074</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920075</v>
+        <v>20330051920378</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920108</v>
+        <v>21330051920075</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920076</v>
+        <v>21330051920108</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920079</v>
+        <v>21330051920076</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920080</v>
+        <v>21330051920079</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920083</v>
+        <v>21330051920080</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920084</v>
+        <v>21330051920083</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920085</v>
+        <v>21330051920084</v>
       </c>
       <c r="B24" t="s">
         <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920086</v>
+        <v>21330051920085</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920302</v>
+        <v>21330051920086</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920089</v>
+        <v>20330051920302</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920092</v>
+        <v>19330051920206</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920093</v>
+        <v>21330051920089</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920096</v>
+        <v>21330051920092</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920097</v>
+        <v>21330051920093</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920099</v>
+        <v>21330051920097</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920101</v>
+        <v>21330051920099</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920383</v>
+        <v>21330051920101</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920102</v>
+        <v>21330051920383</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920104</v>
+        <v>21330051920102</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920106</v>
+        <v>21330051920104</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920107</v>
+        <v>21330051920106</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920387</v>
+        <v>21330051920107</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D39" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>19330051920206</v>
+        <v>21330051920387</v>
       </c>
       <c r="B40" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="D40" t="s">
         <v>164</v>
@@ -6023,7 +5346,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6055,42 +5378,42 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>21330051920078</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>61</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920078</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>60</v>
@@ -6101,22 +5424,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920378</v>
+        <v>21330051920103</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6124,19 +5447,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920378</v>
+        <v>21330051920103</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
@@ -6147,22 +5470,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920077</v>
+        <v>21330051920071</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6170,22 +5493,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920077</v>
+        <v>21330051920072</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6193,45 +5516,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920260</v>
+        <v>20330051920378</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920260</v>
+        <v>21330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6239,22 +5562,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920082</v>
+        <v>21330051920260</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -6265,16 +5588,16 @@
         <v>21330051920082</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>60</v>
@@ -6288,19 +5611,19 @@
         <v>21330051920092</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6308,19 +5631,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920092</v>
+        <v>21330051920094</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>60</v>
@@ -6331,22 +5654,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920094</v>
+        <v>21330051920096</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6354,19 +5677,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920094</v>
+        <v>21330051920098</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>60</v>
@@ -6377,645 +5700,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920098</v>
+        <v>21330051920100</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920098</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920100</v>
-      </c>
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920100</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920072</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920074</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920075</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920108</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920076</v>
-      </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920079</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920080</v>
-      </c>
-      <c r="B26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920083</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920084</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920085</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920086</v>
-      </c>
-      <c r="B30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920302</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>113</v>
-      </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920089</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" t="s">
-        <v>143</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920093</v>
-      </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" t="s">
-        <v>145</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920096</v>
-      </c>
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" t="s">
-        <v>147</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920097</v>
-      </c>
-      <c r="B35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>60</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920099</v>
-      </c>
-      <c r="B36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" t="s">
-        <v>150</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>60</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920101</v>
-      </c>
-      <c r="B37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" t="s">
-        <v>152</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920383</v>
-      </c>
-      <c r="B38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" t="s">
-        <v>93</v>
-      </c>
-      <c r="D38" t="s">
-        <v>153</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920102</v>
-      </c>
-      <c r="B39" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" t="s">
-        <v>154</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920104</v>
-      </c>
-      <c r="B40" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40" t="s">
-        <v>156</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920106</v>
-      </c>
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" t="s">
-        <v>121</v>
-      </c>
-      <c r="D41" t="s">
-        <v>158</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920107</v>
-      </c>
-      <c r="B42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" t="s">
-        <v>122</v>
-      </c>
-      <c r="D42" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>60</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920387</v>
-      </c>
-      <c r="B43" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" t="s">
-        <v>124</v>
-      </c>
-      <c r="D43" t="s">
-        <v>161</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>60</v>
-      </c>
-      <c r="G43">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20221.xlsx
+++ b/grupos/3ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -203,18 +203,18 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
@@ -230,13 +230,73 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
   </si>
   <si>
     <t>FLORES</t>
@@ -245,13 +305,31 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
   </si>
   <si>
     <t>RAMIREZ</t>
@@ -260,22 +338,37 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SANJUAN</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>LAGUNES</t>
@@ -284,37 +377,64 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CAMPOS</t>
+    <t>VALIENTE</t>
   </si>
   <si>
     <t>BRETON</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
     <t>BRAVO</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>TEQUIHUATLE</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
   </si>
   <si>
     <t>ABIGAIL</t>
   </si>
   <si>
-    <t>KATHIA</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>YARED</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -323,184 +443,64 @@
     <t>MIROSLAVA</t>
   </si>
   <si>
-    <t>MARIA TERESA</t>
+    <t>BERENICE</t>
   </si>
   <si>
     <t>VANESSA AMAIRANY</t>
   </si>
   <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
     <t>INGRID AMERICA</t>
   </si>
   <si>
-    <t>JAIME</t>
+    <t>JAZMIN</t>
   </si>
   <si>
     <t>ALDO GEOVANNI</t>
   </si>
   <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
+    <t>CITLALI ESPERANZA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
     <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>ELPIDIO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>GABRIELA</t>
@@ -1001,7 +1001,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>9</v>
@@ -1016,22 +1016,22 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1055,13 +1055,13 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1078,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>-1</v>
@@ -1093,10 +1093,10 @@
         <v>-1</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1132,7 +1132,7 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1170,22 +1170,22 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1206,22 +1206,22 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>-1</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1247,22 +1247,22 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1283,7 +1283,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1298,7 +1298,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1324,22 +1324,22 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1360,22 +1360,22 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1386,7 +1386,7 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -1401,22 +1401,22 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1437,10 +1437,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1478,22 +1478,22 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1517,7 +1517,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1555,22 +1555,22 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1591,22 +1591,22 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>7</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1632,22 +1632,22 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1671,7 +1671,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1709,22 +1709,22 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1748,10 +1748,10 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1771,7 +1771,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>8</v>
@@ -1786,22 +1786,22 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1825,19 +1825,19 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1848,7 +1848,7 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -1863,22 +1863,22 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1899,16 +1899,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1940,22 +1940,22 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1979,7 +1979,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -2017,16 +2017,16 @@
         <v>-1</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2053,16 +2053,16 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2094,22 +2094,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2133,13 +2133,13 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2171,22 +2171,22 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2207,10 +2207,10 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2248,22 +2248,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2325,22 +2325,22 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2364,19 +2364,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2402,22 +2402,22 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2438,22 +2438,22 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2479,22 +2479,22 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2515,13 +2515,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>7</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2544,10 +2544,10 @@
         <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2559,7 +2559,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2585,22 +2585,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2624,13 +2624,13 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>8</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2662,22 +2662,22 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2698,16 +2698,16 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2739,22 +2739,22 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2778,7 +2778,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2816,22 +2816,22 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2867,7 +2867,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2878,7 +2878,7 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -2893,22 +2893,22 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2929,22 +2929,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2970,22 +2970,22 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3012,7 +3012,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3021,7 +3021,7 @@
         <v>-1</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3032,7 +3032,7 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -3047,22 +3047,22 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3086,7 +3086,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3124,22 +3124,22 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3163,13 +3163,13 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>8</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3186,7 +3186,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>8</v>
@@ -3201,22 +3201,22 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3237,16 +3237,16 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3278,22 +3278,22 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3317,13 +3317,13 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3355,22 +3355,22 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3394,19 +3394,19 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>8</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3432,22 +3432,22 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3468,7 +3468,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U36">
         <v>6</v>
@@ -3477,7 +3477,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>8</v>
@@ -3494,7 +3494,7 @@
         <v>5</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>8</v>
@@ -3509,22 +3509,22 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3545,22 +3545,22 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3571,7 +3571,7 @@
         <v>5</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>7</v>
@@ -3586,16 +3586,16 @@
         <v>-1</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>-1</v>
@@ -3622,13 +3622,13 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3663,22 +3663,22 @@
         <v>9</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3702,7 +3702,7 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>8</v>
@@ -3740,22 +3740,22 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3776,13 +3776,13 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -3802,7 +3802,7 @@
         <v>5</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -3817,16 +3817,16 @@
         <v>-1</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L41">
         <v>-1</v>
@@ -3853,16 +3853,16 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X41">
         <v>-1</v>
@@ -3894,22 +3894,22 @@
         <v>9</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
         <v>-1</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3933,19 +3933,19 @@
         <v>7</v>
       </c>
       <c r="U42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V42">
         <v>9</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>7</v>
       </c>
       <c r="Y42">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4010,30 +4010,30 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>81.58</v>
+      </c>
+      <c r="G2">
+        <v>18.42</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>71.05</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.1</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
-      <c r="J2">
-        <v>28.95</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -4045,59 +4045,59 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>81.58</v>
       </c>
       <c r="G3">
-        <v>18.42</v>
+        <v>7.89</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>89.47</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>10.53</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>4</v>
@@ -4129,34 +4129,34 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>94.87</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G6">
-        <v>2.56</v>
+        <v>5.26</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4182,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -4198,7 +4198,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4227,42 +4227,42 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920071</v>
+        <v>21330051920072</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920072</v>
+        <v>20330051920222</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4270,19 +4270,19 @@
         <v>20330051920222</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4290,19 +4290,19 @@
         <v>20330051920222</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4310,339 +4310,119 @@
         <v>20330051920222</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920222</v>
+        <v>21330051920260</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920222</v>
+        <v>21330051920096</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
         <v>85</v>
       </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920077</v>
+        <v>21330051920105</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
         <v>86</v>
       </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920078</v>
+        <v>21330051920109</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
         <v>87</v>
       </c>
-      <c r="D10" t="s">
-        <v>100</v>
-      </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920260</v>
+        <v>21330051920109</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920082</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920094</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920096</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920098</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920103</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920105</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920105</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920109</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920109</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920109</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4681,16 +4461,16 @@
         <v>20330051920222</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4698,47 +4478,47 @@
         <v>21330051920109</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920105</v>
+        <v>21330051920072</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920071</v>
+        <v>21330051920260</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4746,16 +4526,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920072</v>
+        <v>21330051920096</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4763,16 +4543,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920077</v>
+        <v>21330051920105</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" t="s">
         <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>99</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4780,149 +4560,149 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920078</v>
+        <v>21330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920260</v>
+        <v>21330051920074</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920082</v>
+        <v>20330051920378</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920094</v>
+        <v>21330051920075</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920096</v>
+        <v>21330051920108</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920098</v>
+        <v>21330051920076</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920100</v>
+        <v>21330051920077</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920103</v>
+        <v>21330051920078</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920074</v>
+        <v>21330051920079</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
         <v>141</v>
@@ -4933,16 +4713,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920378</v>
+        <v>21330051920080</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4950,16 +4730,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920075</v>
+        <v>21330051920082</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4967,16 +4747,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920108</v>
+        <v>21330051920083</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4984,16 +4764,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920076</v>
+        <v>21330051920084</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5001,16 +4781,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920079</v>
+        <v>21330051920085</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5018,16 +4798,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920080</v>
+        <v>21330051920086</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5035,13 +4815,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920083</v>
+        <v>20330051920302</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
         <v>147</v>
@@ -5052,13 +4832,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920084</v>
+        <v>19330051920206</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
         <v>148</v>
@@ -5069,13 +4849,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920085</v>
+        <v>21330051920089</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
         <v>149</v>
@@ -5086,13 +4866,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920086</v>
+        <v>21330051920092</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
         <v>150</v>
@@ -5103,13 +4883,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920302</v>
+        <v>21330051920093</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>151</v>
@@ -5120,13 +4900,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920206</v>
+        <v>21330051920094</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
         <v>152</v>
@@ -5137,13 +4917,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920089</v>
+        <v>21330051920097</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>153</v>
@@ -5154,13 +4934,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920092</v>
+        <v>21330051920098</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
         <v>154</v>
@@ -5171,13 +4951,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920093</v>
+        <v>21330051920099</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
         <v>155</v>
@@ -5188,13 +4968,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920097</v>
+        <v>21330051920100</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s">
         <v>156</v>
@@ -5205,13 +4985,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920099</v>
+        <v>21330051920101</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
         <v>157</v>
@@ -5222,13 +5002,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920101</v>
+        <v>21330051920383</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
         <v>158</v>
@@ -5239,13 +5019,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920383</v>
+        <v>21330051920102</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
         <v>159</v>
@@ -5256,13 +5036,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920102</v>
+        <v>21330051920103</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
         <v>160</v>
@@ -5276,10 +5056,10 @@
         <v>21330051920104</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
         <v>161</v>
@@ -5293,10 +5073,10 @@
         <v>21330051920106</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
         <v>162</v>
@@ -5310,10 +5090,10 @@
         <v>21330051920107</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D39" t="s">
         <v>163</v>
@@ -5327,10 +5107,10 @@
         <v>21330051920387</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
         <v>164</v>
@@ -5346,7 +5126,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5378,22 +5158,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920078</v>
+        <v>21330051920077</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5401,45 +5181,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920078</v>
+        <v>21330051920077</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920103</v>
+        <v>21330051920086</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5447,68 +5227,68 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920103</v>
+        <v>21330051920086</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920071</v>
+        <v>21330051920105</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920072</v>
+        <v>21330051920105</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5516,22 +5296,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920378</v>
+        <v>21330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5539,16 +5319,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920077</v>
+        <v>21330051920080</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5557,167 +5337,29 @@
         <v>60</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920260</v>
+        <v>21330051920096</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>63</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920082</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920092</v>
-      </c>
-      <c r="B12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920094</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920096</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920098</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20221.xlsx
+++ b/grupos/3ALCV - Estadisticos 20221.xlsx
@@ -1028,7 +1028,7 @@
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -1259,7 +1259,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -1336,7 +1336,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1372,7 +1372,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1413,7 +1413,7 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1526,7 +1526,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1567,7 +1567,7 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1644,7 +1644,7 @@
         <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1721,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -1798,7 +1798,7 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -1952,7 +1952,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>8</v>
@@ -2106,7 +2106,7 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -2142,7 +2142,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2183,7 +2183,7 @@
         <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -2260,7 +2260,7 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2337,7 +2337,7 @@
         <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -2491,7 +2491,7 @@
         <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -2597,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>7</v>
@@ -2674,7 +2674,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>6</v>
@@ -2751,7 +2751,7 @@
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -2828,7 +2828,7 @@
         <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -3059,7 +3059,7 @@
         <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>8</v>
@@ -3136,7 +3136,7 @@
         <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>6</v>
@@ -3172,7 +3172,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3213,7 +3213,7 @@
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>6</v>
@@ -3249,7 +3249,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3290,7 +3290,7 @@
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>9</v>
@@ -3367,7 +3367,7 @@
         <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -3444,7 +3444,7 @@
         <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -3675,7 +3675,7 @@
         <v>9</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>8</v>
@@ -3711,7 +3711,7 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>9</v>
@@ -3752,7 +3752,7 @@
         <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
         <v>8</v>
@@ -3788,7 +3788,7 @@
         <v>9</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -3906,7 +3906,7 @@
         <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M42">
         <v>6</v>
@@ -3942,7 +3942,7 @@
         <v>10</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>8</v>

--- a/grupos/3ALCV - Estadisticos 20221.xlsx
+++ b/grupos/3ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -203,15 +203,15 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -230,286 +230,286 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>CHACÓN</t>
   </si>
   <si>
-    <t>CAMARILLO</t>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>SORIA</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
   </si>
   <si>
     <t>CAMPOS</t>
   </si>
   <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
     <t>MENA</t>
   </si>
   <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
     <t>KATHIA</t>
   </si>
   <si>
-    <t>ARIEL</t>
+    <t>CRISTAL YOSELIN</t>
+  </si>
+  <si>
+    <t>REYLI</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>BERENICE</t>
   </si>
   <si>
     <t>MARIA TERESA</t>
   </si>
   <si>
+    <t>VANESSA AMAIRANY</t>
+  </si>
+  <si>
+    <t>REGINA ISABEL</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>DIANA IVONNE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>FATIMA MARILYN</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ITZEL ABIGAIL</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
     <t>JAIME</t>
   </si>
   <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>ALDO GEOVANNI</t>
+  </si>
+  <si>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>CITLALI ESPERANZA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>ELPIDIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>CRISTAL YOSELIN</t>
-  </si>
-  <si>
-    <t>REYLI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>YARED</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>BERENICE</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>REGINA ISABEL</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>DIANA IVONNE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>FATIMA MARILYN</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ITZEL ABIGAIL</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>CITLALI ESPERANZA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>RUBI</t>
   </si>
   <si>
     <t>FLOR GUADALUPE</t>
@@ -1081,16 +1081,16 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1099,16 +1099,16 @@
         <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1135,16 +1135,16 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>-1</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1164,7 +1164,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1218,7 +1218,7 @@
         <v>5</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1875,7 +1875,7 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -1911,7 +1911,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -2014,7 +2014,7 @@
         <v>7</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>6</v>
@@ -2029,10 +2029,10 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2065,10 +2065,10 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2414,7 +2414,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2450,7 +2450,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2905,7 +2905,7 @@
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -2941,7 +2941,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2964,7 +2964,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>9</v>
@@ -2982,7 +2982,7 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3018,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3521,7 +3521,7 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>5</v>
@@ -3557,7 +3557,7 @@
         <v>7</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y37">
         <v>7</v>
@@ -3583,7 +3583,7 @@
         <v>6</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>7</v>
@@ -3598,10 +3598,10 @@
         <v>5</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3637,7 +3637,7 @@
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3811,10 +3811,10 @@
         <v>6</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <v>7</v>
@@ -3829,10 +3829,10 @@
         <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3865,10 +3865,10 @@
         <v>5</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -4033,7 +4033,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -4042,89 +4042,89 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>81.58</v>
+        <v>86.84</v>
       </c>
       <c r="G3">
-        <v>7.89</v>
+        <v>13.16</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>87.18000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="G4">
-        <v>10.26</v>
+        <v>13.16</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
       </c>
       <c r="C5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>89.47</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>10.26</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>10.53</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4173,22 +4173,22 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>97.44</v>
       </c>
       <c r="G7">
+        <v>2.56</v>
+      </c>
+      <c r="H7">
+        <v>7.5</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>7.6</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
       <c r="J7">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4198,7 +4198,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4227,202 +4227,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920072</v>
+        <v>20330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920222</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920222</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920222</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920222</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920260</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920096</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920105</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920109</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920109</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4461,33 +4281,33 @@
         <v>20330051920222</v>
       </c>
       <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920109</v>
+        <v>21330051920071</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4495,78 +4315,78 @@
         <v>21330051920072</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920260</v>
+        <v>21330051920074</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920096</v>
+        <v>20330051920378</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920105</v>
+        <v>21330051920075</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920071</v>
+        <v>21330051920108</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
         <v>133</v>
@@ -4577,13 +4397,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920074</v>
+        <v>21330051920076</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>134</v>
@@ -4594,13 +4414,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920378</v>
+        <v>21330051920077</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
         <v>135</v>
@@ -4611,13 +4431,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920075</v>
+        <v>21330051920078</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
         <v>136</v>
@@ -4628,13 +4448,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920108</v>
+        <v>21330051920079</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
         <v>137</v>
@@ -4645,13 +4465,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920076</v>
+        <v>21330051920260</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
         <v>138</v>
@@ -4662,16 +4482,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920077</v>
+        <v>21330051920080</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4679,16 +4499,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920078</v>
+        <v>21330051920082</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4696,16 +4516,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920079</v>
+        <v>21330051920083</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4713,16 +4533,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920080</v>
+        <v>21330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4730,13 +4550,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920082</v>
+        <v>21330051920085</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
         <v>142</v>
@@ -4747,13 +4567,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920083</v>
+        <v>21330051920086</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
         <v>143</v>
@@ -4764,13 +4584,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920084</v>
+        <v>20330051920302</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
         <v>144</v>
@@ -4781,13 +4601,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920085</v>
+        <v>19330051920206</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>145</v>
@@ -4798,13 +4618,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920086</v>
+        <v>21330051920089</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
         <v>146</v>
@@ -4815,13 +4635,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920302</v>
+        <v>21330051920092</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
         <v>147</v>
@@ -4832,13 +4652,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920206</v>
+        <v>21330051920093</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>148</v>
@@ -4849,13 +4669,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920089</v>
+        <v>21330051920094</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>149</v>
@@ -4866,13 +4686,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920092</v>
+        <v>21330051920096</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
         <v>150</v>
@@ -4883,13 +4703,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920093</v>
+        <v>21330051920097</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>151</v>
@@ -4900,13 +4720,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920094</v>
+        <v>21330051920098</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
         <v>152</v>
@@ -4917,13 +4737,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920097</v>
+        <v>21330051920099</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
         <v>153</v>
@@ -4934,13 +4754,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920098</v>
+        <v>21330051920100</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
         <v>154</v>
@@ -4951,13 +4771,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920099</v>
+        <v>21330051920101</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
         <v>155</v>
@@ -4968,13 +4788,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920100</v>
+        <v>21330051920383</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
         <v>156</v>
@@ -4985,13 +4805,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920101</v>
+        <v>21330051920102</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
         <v>157</v>
@@ -5002,13 +4822,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920383</v>
+        <v>21330051920103</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
         <v>158</v>
@@ -5019,13 +4839,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920102</v>
+        <v>21330051920104</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
         <v>159</v>
@@ -5036,13 +4856,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920103</v>
+        <v>21330051920105</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
         <v>160</v>
@@ -5053,13 +4873,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920104</v>
+        <v>21330051920106</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
         <v>161</v>
@@ -5070,13 +4890,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920106</v>
+        <v>21330051920107</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D38" t="s">
         <v>162</v>
@@ -5087,13 +4907,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920107</v>
+        <v>21330051920109</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
         <v>163</v>
@@ -5107,10 +4927,10 @@
         <v>21330051920387</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
         <v>164</v>
@@ -5126,7 +4946,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5161,13 +4981,13 @@
         <v>21330051920077</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5184,19 +5004,19 @@
         <v>21330051920077</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5204,22 +5024,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920086</v>
+        <v>21330051920109</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5227,19 +5047,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920086</v>
+        <v>21330051920109</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>61</v>
@@ -5250,22 +5070,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920105</v>
+        <v>21330051920078</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5273,45 +5093,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920105</v>
+        <v>21330051920080</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920078</v>
+        <v>21330051920103</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5319,48 +5139,25 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920080</v>
+        <v>21330051920105</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920096</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3ALCV - Estadisticos 20221.xlsx
+++ b/grupos/3ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -230,184 +230,184 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CHACÓN</t>
+  </si>
+  <si>
     <t>CAMARILLO</t>
   </si>
   <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>SORIA</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>QUIÑONES</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>KATHIA</t>
+  </si>
+  <si>
     <t>ARIEL</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CHACÓN</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>ELPIDIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>LEÓN</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>KATHIA</t>
   </si>
   <si>
     <t>CRISTAL YOSELIN</t>
@@ -1084,7 +1084,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1102,7 +1102,7 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -4109,22 +4109,22 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>87.18000000000001</v>
       </c>
       <c r="G5">
-        <v>10.26</v>
+        <v>12.82</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4198,7 +4198,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4223,26 +4223,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920222</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4278,30 +4258,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920222</v>
+        <v>21330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920071</v>
+        <v>21330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
         <v>128</v>
@@ -4312,13 +4292,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920072</v>
+        <v>20330051920222</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
         <v>129</v>
@@ -4332,10 +4312,10 @@
         <v>21330051920074</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
         <v>130</v>
@@ -4349,10 +4329,10 @@
         <v>20330051920378</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
         <v>131</v>
@@ -4366,10 +4346,10 @@
         <v>21330051920075</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
         <v>132</v>
@@ -4383,10 +4363,10 @@
         <v>21330051920108</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>133</v>
@@ -4400,10 +4380,10 @@
         <v>21330051920076</v>
       </c>
       <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
         <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>134</v>
@@ -4417,10 +4397,10 @@
         <v>21330051920077</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
         <v>135</v>
@@ -4434,10 +4414,10 @@
         <v>21330051920078</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
         <v>136</v>
@@ -4451,10 +4431,10 @@
         <v>21330051920079</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
         <v>137</v>
@@ -4468,10 +4448,10 @@
         <v>21330051920260</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
         <v>138</v>
@@ -4485,10 +4465,10 @@
         <v>21330051920080</v>
       </c>
       <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
         <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
       </c>
       <c r="D14" t="s">
         <v>135</v>
@@ -4502,10 +4482,10 @@
         <v>21330051920082</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
         <v>139</v>
@@ -4519,10 +4499,10 @@
         <v>21330051920083</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
         <v>140</v>
@@ -4536,10 +4516,10 @@
         <v>21330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
         <v>141</v>
@@ -4553,10 +4533,10 @@
         <v>21330051920085</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
         <v>142</v>
@@ -4570,10 +4550,10 @@
         <v>21330051920086</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
         <v>143</v>
@@ -4587,10 +4567,10 @@
         <v>20330051920302</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
         <v>144</v>
@@ -4604,10 +4584,10 @@
         <v>19330051920206</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
         <v>145</v>
@@ -4621,10 +4601,10 @@
         <v>21330051920089</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>146</v>
@@ -4638,10 +4618,10 @@
         <v>21330051920092</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
         <v>147</v>
@@ -4655,10 +4635,10 @@
         <v>21330051920093</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
         <v>148</v>
@@ -4672,10 +4652,10 @@
         <v>21330051920094</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
         <v>149</v>
@@ -4689,10 +4669,10 @@
         <v>21330051920096</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
         <v>150</v>
@@ -4706,10 +4686,10 @@
         <v>21330051920097</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
         <v>151</v>
@@ -4723,10 +4703,10 @@
         <v>21330051920098</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
         <v>152</v>
@@ -4740,10 +4720,10 @@
         <v>21330051920099</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
         <v>153</v>
@@ -4757,10 +4737,10 @@
         <v>21330051920100</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
         <v>154</v>
@@ -4774,10 +4754,10 @@
         <v>21330051920101</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
         <v>155</v>
@@ -4791,10 +4771,10 @@
         <v>21330051920383</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
         <v>156</v>
@@ -4808,10 +4788,10 @@
         <v>21330051920102</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
         <v>157</v>
@@ -4825,10 +4805,10 @@
         <v>21330051920103</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D34" t="s">
         <v>158</v>
@@ -4842,10 +4822,10 @@
         <v>21330051920104</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>159</v>
@@ -4859,10 +4839,10 @@
         <v>21330051920105</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
         <v>160</v>
@@ -4876,10 +4856,10 @@
         <v>21330051920106</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D37" t="s">
         <v>161</v>
@@ -4893,10 +4873,10 @@
         <v>21330051920107</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s">
         <v>162</v>
@@ -4910,10 +4890,10 @@
         <v>21330051920109</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D39" t="s">
         <v>163</v>
@@ -4927,10 +4907,10 @@
         <v>21330051920387</v>
       </c>
       <c r="B40" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D40" t="s">
         <v>164</v>
@@ -4981,10 +4961,10 @@
         <v>21330051920077</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
         <v>135</v>
@@ -5004,10 +4984,10 @@
         <v>21330051920077</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
         <v>135</v>
@@ -5027,10 +5007,10 @@
         <v>21330051920109</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
         <v>163</v>
@@ -5050,10 +5030,10 @@
         <v>21330051920109</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
         <v>163</v>
@@ -5073,10 +5053,10 @@
         <v>21330051920078</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
         <v>136</v>
@@ -5096,10 +5076,10 @@
         <v>21330051920080</v>
       </c>
       <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
         <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
       </c>
       <c r="D7" t="s">
         <v>135</v>
@@ -5119,10 +5099,10 @@
         <v>21330051920103</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
         <v>158</v>
@@ -5142,10 +5122,10 @@
         <v>21330051920105</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
         <v>160</v>

--- a/grupos/3ALCV - Estadisticos 20221.xlsx
+++ b/grupos/3ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -203,19 +203,19 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
   </si>
   <si>
     <t>NC</t>
@@ -1034,28 +1034,28 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>10</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1067,7 +1067,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1111,22 +1111,22 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1188,22 +1188,22 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>5</v>
@@ -1212,13 +1212,13 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>5</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1265,22 +1265,22 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1342,40 +1342,40 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1419,37 +1419,37 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>9</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1496,22 +1496,22 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1529,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1573,22 +1573,22 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1597,13 +1597,13 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1650,22 +1650,22 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1727,28 +1727,28 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1804,28 +1804,28 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1837,7 +1837,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1881,25 +1881,25 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>5</v>
@@ -1958,31 +1958,31 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1991,7 +1991,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2035,28 +2035,28 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -2068,7 +2068,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2112,31 +2112,31 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2189,22 +2189,22 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2219,7 +2219,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2266,22 +2266,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2343,22 +2343,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2367,7 +2367,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2420,25 +2420,25 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2450,7 +2450,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2497,22 +2497,22 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2530,7 +2530,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2550,13 +2550,13 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2603,22 +2603,22 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2680,25 +2680,25 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2713,7 +2713,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2757,28 +2757,28 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>10</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2834,25 +2834,25 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2911,40 +2911,40 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>6</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2988,22 +2988,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3021,7 +3021,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3065,28 +3065,28 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3095,7 +3095,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3142,37 +3142,37 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>8</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3219,22 +3219,22 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3243,7 +3243,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3252,7 +3252,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3296,22 +3296,22 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3320,7 +3320,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3373,28 +3373,28 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>9</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3406,7 +3406,7 @@
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3450,22 +3450,22 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3480,7 +3480,7 @@
         <v>9</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3527,40 +3527,40 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>7</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3604,25 +3604,25 @@
         <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3637,7 +3637,7 @@
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3681,22 +3681,22 @@
         <v>8</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3758,40 +3758,40 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q40">
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T40">
         <v>8</v>
       </c>
       <c r="U40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>9</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3835,28 +3835,28 @@
         <v>6</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q41">
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -3865,7 +3865,7 @@
         <v>5</v>
       </c>
       <c r="X41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y41">
         <v>6</v>
@@ -3912,25 +3912,25 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q42">
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U42">
         <v>9</v>
@@ -4010,19 +4010,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>81.58</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G2">
-        <v>18.42</v>
+        <v>15.79</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4033,28 +4033,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>86.84</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="G3">
-        <v>13.16</v>
+        <v>12.82</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4074,19 +4074,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="G4">
-        <v>13.16</v>
+        <v>10.53</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -4106,19 +4106,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>87.18000000000001</v>
+        <v>92.31</v>
       </c>
       <c r="G5">
-        <v>12.82</v>
+        <v>7.69</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4150,7 +4150,7 @@
         <v>5.26</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4161,28 +4161,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>97.44</v>
+        <v>97.37</v>
       </c>
       <c r="G7">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4926,7 +4926,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4958,16 +4958,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920077</v>
+        <v>21330051920086</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4981,16 +4981,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920077</v>
+        <v>21330051920086</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5004,22 +5004,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920109</v>
+        <v>21330051920094</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5027,22 +5027,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920109</v>
+        <v>21330051920094</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5050,16 +5050,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920078</v>
+        <v>21330051920109</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5073,22 +5073,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920080</v>
+        <v>21330051920109</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5096,22 +5096,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920103</v>
+        <v>21330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5119,24 +5119,70 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>21330051920260</v>
+      </c>
+      <c r="B9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920092</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
         <v>21330051920105</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>97</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C11" t="s">
         <v>122</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D11" t="s">
         <v>160</v>
       </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9">
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCV - Estadisticos 20221.xlsx
+++ b/grupos/3ALCV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="165">
   <si>
     <t>Materia</t>
   </si>
@@ -203,10 +203,10 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
     <t>Flores Ovalle Victor</t>
@@ -1043,7 +1043,7 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>9</v>
@@ -1061,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1120,7 +1120,7 @@
         <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -1197,7 +1197,7 @@
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>7</v>
@@ -1274,7 +1274,7 @@
         <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1351,7 +1351,7 @@
         <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -1369,7 +1369,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -1505,7 +1505,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1582,7 +1582,7 @@
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1659,7 +1659,7 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>10</v>
@@ -1736,7 +1736,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -1754,7 +1754,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1813,7 +1813,7 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>7</v>
@@ -1890,7 +1890,7 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>6</v>
@@ -1967,7 +1967,7 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -2044,7 +2044,7 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>7</v>
@@ -2062,7 +2062,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -2121,7 +2121,7 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -2198,7 +2198,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -2275,7 +2275,7 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -2352,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>9</v>
@@ -2429,7 +2429,7 @@
         <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -2447,7 +2447,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2506,7 +2506,7 @@
         <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -2553,7 +2553,7 @@
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2612,7 +2612,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2689,7 +2689,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -2707,7 +2707,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2766,7 +2766,7 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -2843,7 +2843,7 @@
         <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -2920,7 +2920,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>5</v>
@@ -2938,7 +2938,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -2997,7 +2997,7 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -3074,7 +3074,7 @@
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>7</v>
@@ -3092,7 +3092,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -3169,7 +3169,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3228,7 +3228,7 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>8</v>
@@ -3305,7 +3305,7 @@
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3382,7 +3382,7 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
@@ -3459,7 +3459,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>6</v>
@@ -3477,7 +3477,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3536,7 +3536,7 @@
         <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
         <v>7</v>
@@ -3554,7 +3554,7 @@
         <v>6</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>6</v>
@@ -3613,7 +3613,7 @@
         <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
         <v>6</v>
@@ -3690,7 +3690,7 @@
         <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>7</v>
@@ -3767,7 +3767,7 @@
         <v>5</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
         <v>9</v>
@@ -3844,7 +3844,7 @@
         <v>7</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R41">
         <v>8</v>
@@ -3862,7 +3862,7 @@
         <v>7</v>
       </c>
       <c r="W41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>6</v>
@@ -3921,7 +3921,7 @@
         <v>9</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>10</v>
@@ -4033,28 +4033,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>34</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>87.18000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="G3">
-        <v>12.82</v>
+        <v>10.53</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4065,28 +4065,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>89.47</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="G4">
-        <v>10.53</v>
+        <v>10.26</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4926,7 +4926,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4996,7 +4996,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5004,16 +5004,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920094</v>
+        <v>21330051920078</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5027,22 +5027,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920094</v>
+        <v>21330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5050,22 +5050,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920109</v>
+        <v>21330051920105</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5085,104 +5085,12 @@
         <v>163</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920078</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920260</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920092</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920105</v>
-      </c>
-      <c r="B11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" t="s">
-        <v>160</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>
